--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -647,12 +647,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|2</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
         <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
         <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5|19|22|26|38|45|30</t>
+          <t>17|19|20|31|38|44|15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
         <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -843,12 +843,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6|16|24|31|41|45|12</t>
+          <t>5|13|24|30|41|48|47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L6" t="n">
+        <v>44</v>
+      </c>
+      <c r="M6" t="n">
         <v>45</v>
       </c>
-      <c r="M6" t="n">
-        <v>46</v>
-      </c>
       <c r="N6" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="O6" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|19|24|26|45|46|17</t>
+          <t>9|11|14|40|44|45|37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1079,25 +1079,25 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="O7" t="n">
         <v>163</v>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|13|24|32|41|48|18</t>
+          <t>2|9|24|40|43|45|34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="O8" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|9|14|26|40|41|24</t>
+          <t>2|9|24|31|41|44|33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M9" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
         <v>48</v>
       </c>
       <c r="O9" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6|19|24|31|40|47|48</t>
+          <t>3|13|24|26|32|41|48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="O10" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2|11|13|26|39|40|7</t>
+          <t>1|5|9|30|38|44|27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1471,37 +1471,37 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="n">
         <v>13</v>
-      </c>
-      <c r="J11" t="n">
-        <v>20</v>
       </c>
       <c r="K11" t="n">
         <v>26</v>
       </c>
       <c r="L11" t="n">
+        <v>39</v>
+      </c>
+      <c r="M11" t="n">
+        <v>40</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>131</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>38</v>
-      </c>
-      <c r="M11" t="n">
-        <v>41</v>
-      </c>
-      <c r="N11" t="n">
-        <v>35</v>
-      </c>
-      <c r="O11" t="n">
-        <v>143</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>36</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5|13|20|26|38|41|35</t>
+          <t>2|11|13|26|39|40|7</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>
@@ -1569,37 +1569,37 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M12" t="n">
+        <v>43</v>
+      </c>
+      <c r="N12" t="n">
+        <v>18</v>
+      </c>
+      <c r="O12" t="n">
+        <v>145</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
         <v>41</v>
-      </c>
-      <c r="N12" t="n">
-        <v>16</v>
-      </c>
-      <c r="O12" t="n">
-        <v>147</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>36</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5|8|24|30|39|41|16</t>
+          <t>2|16|24|29|31|43|18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4375</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|2</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -687,37 +687,37 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
+        <v>45</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>153</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>44</v>
-      </c>
-      <c r="N3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O3" t="n">
-        <v>169</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>27</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6667</v>
+        <v>48.4375</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>17|19|20|31|38|44|15</t>
+          <t>1|9|24|30|44|45|4</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6667</v>
+        <v>43.4375</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|47</t>
+          <t>9|16|22|31|44|45|7</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -883,37 +883,37 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
+        <v>26</v>
+      </c>
+      <c r="L5" t="n">
+        <v>38</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40</v>
+      </c>
+      <c r="N5" t="n">
+        <v>35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>141</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
         <v>31</v>
-      </c>
-      <c r="L5" t="n">
-        <v>40</v>
-      </c>
-      <c r="M5" t="n">
-        <v>45</v>
-      </c>
-      <c r="N5" t="n">
-        <v>30</v>
-      </c>
-      <c r="O5" t="n">
-        <v>157</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>43</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1667</v>
+        <v>40.9375</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|19|20|31|40|45|30</t>
+          <t>9|11|17|26|38|40|35</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
         <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6667</v>
+        <v>39.4375</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|11|14|40|44|45|37</t>
+          <t>1|7|24|26|38|45|5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1079,25 +1079,25 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L7" t="n">
+        <v>41</v>
+      </c>
+      <c r="M7" t="n">
         <v>43</v>
       </c>
-      <c r="M7" t="n">
-        <v>45</v>
-      </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>163</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6667</v>
+        <v>38.4375</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|34</t>
+          <t>6|16|24|33|41|43|2</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L8" t="n">
         <v>41</v>
       </c>
       <c r="M8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N8" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.95241428571428</v>
+        <v>37.72321428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|33</t>
+          <t>2|19|24|39|41|42|7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="O9" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4167</v>
+        <v>37.1875</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|13|24|26|32|41|48</t>
+          <t>1|19|24|38|40|45|42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1373,37 +1373,37 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M10" t="n">
+        <v>49</v>
+      </c>
+      <c r="N10" t="n">
+        <v>13</v>
+      </c>
+      <c r="O10" t="n">
+        <v>165</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>44</v>
-      </c>
-      <c r="N10" t="n">
-        <v>27</v>
-      </c>
-      <c r="O10" t="n">
-        <v>127</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.00003333333333</v>
+        <v>36.77083333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1|5|9|30|38|44|27</t>
+          <t>5|9|14|40|48|49|13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1471,37 +1471,37 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M11" t="n">
+        <v>45</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>151</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>40</v>
-      </c>
-      <c r="N11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>131</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>38</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6667</v>
+        <v>36.4375</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2|11|13|26|39|40|7</t>
+          <t>5|9|22|30|40|45|1</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="O12" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.39397272727273</v>
+        <v>36.16477272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|16|24|29|31|43|18</t>
+          <t>6|18|19|31|39|44|48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4375</v>
+        <v>74.625</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|5|44|46|49|41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -687,37 +687,37 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M3" t="n">
+        <v>47</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
+        <v>163</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>45</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>153</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>44</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.4375</v>
+        <v>48.625</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|9|24|30|44|45|4</t>
+          <t>2|19|24|31|40|47|10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -785,16 +785,16 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
         <v>9</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
         <v>44</v>
@@ -803,10 +803,10 @@
         <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.4375</v>
+        <v>43.625</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9|16|22|31|44|45|7</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
         <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M5" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.9375</v>
+        <v>41.125</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|11|17|26|38|40|35</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
+        <v>16</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K6" t="n">
+        <v>37</v>
+      </c>
+      <c r="L6" t="n">
+        <v>41</v>
+      </c>
+      <c r="M6" t="n">
+        <v>44</v>
+      </c>
+      <c r="N6" t="n">
         <v>7</v>
       </c>
-      <c r="J6" t="n">
-        <v>24</v>
-      </c>
-      <c r="K6" t="n">
-        <v>26</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
+        <v>163</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
         <v>38</v>
-      </c>
-      <c r="M6" t="n">
-        <v>45</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>141</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>44</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.4375</v>
+        <v>39.625</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1|7|24|26|38|45|5</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1079,10 +1079,10 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
@@ -1091,16 +1091,16 @@
         <v>33</v>
       </c>
       <c r="L7" t="n">
+        <v>38</v>
+      </c>
+      <c r="M7" t="n">
         <v>41</v>
       </c>
-      <c r="M7" t="n">
-        <v>43</v>
-      </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.4375</v>
+        <v>38.625</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|16|24|33|41|43|2</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1180,34 +1180,34 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
         <v>41</v>
       </c>
       <c r="M8" t="n">
+        <v>44</v>
+      </c>
+      <c r="N8" t="n">
+        <v>32</v>
+      </c>
+      <c r="O8" t="n">
+        <v>151</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>42</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>167</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>40</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.72321428571428</v>
+        <v>37.91071428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|19|24|39|41|42|7</t>
+          <t>2|9|24|31|41|44|32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>19</v>
@@ -1284,19 +1284,19 @@
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
+        <v>31</v>
+      </c>
+      <c r="M9" t="n">
         <v>40</v>
       </c>
-      <c r="M9" t="n">
-        <v>45</v>
-      </c>
       <c r="N9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O9" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.1875</v>
+        <v>37.375</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|19|24|38|40|45|42</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
+        <v>32</v>
+      </c>
+      <c r="M10" t="n">
+        <v>41</v>
+      </c>
+      <c r="N10" t="n">
         <v>48</v>
       </c>
-      <c r="M10" t="n">
-        <v>49</v>
-      </c>
-      <c r="N10" t="n">
-        <v>13</v>
-      </c>
       <c r="O10" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.77083333333333</v>
+        <v>36.95833333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>5|9|14|40|48|49|13</t>
+          <t>3|13|24|26|32|41|48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
+        <v>38</v>
+      </c>
+      <c r="M11" t="n">
         <v>40</v>
       </c>
-      <c r="M11" t="n">
-        <v>45</v>
-      </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="O11" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.4375</v>
+        <v>36.625</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5|9|22|30|40|45|1</t>
+          <t>17|19|24|27|38|40|33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L12" t="n">
         <v>39</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N12" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.16477272727273</v>
+        <v>36.35227272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6|18|19|31|39|44|48</t>
+          <t>17|20|24|29|39|40|7</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.625</v>
+        <v>74.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|41</t>
+          <t>1|3|5|44|46|49|34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
         <v>40</v>
       </c>
       <c r="M3" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.625</v>
+        <v>48.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2|19|24|31|40|47|10</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
         <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.625</v>
+        <v>43.75</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>2|16|19|37|44|49|26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
         <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
         <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.125</v>
+        <v>41.25</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>7|19|20|30|44|45|15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="O6" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.625</v>
+        <v>39.75</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>5|9|24|30|44|45|32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M7" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.625</v>
+        <v>38.75</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
+        <v>26</v>
+      </c>
+      <c r="L8" t="n">
         <v>31</v>
       </c>
-      <c r="L8" t="n">
-        <v>41</v>
-      </c>
       <c r="M8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N8" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.91071428571428</v>
+        <v>38.03571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|32</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.375</v>
+        <v>37.5</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="O10" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.95833333333333</v>
+        <v>37.08333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|13|24|26|32|41|48</t>
+          <t>2|9|24|40|43|45|33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1471,37 +1471,37 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
+        <v>16</v>
+      </c>
+      <c r="J11" t="n">
         <v>19</v>
       </c>
-      <c r="J11" t="n">
-        <v>24</v>
-      </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
+        <v>41</v>
+      </c>
+      <c r="M11" t="n">
+        <v>44</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>163</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>38</v>
-      </c>
-      <c r="M11" t="n">
-        <v>40</v>
-      </c>
-      <c r="N11" t="n">
-        <v>33</v>
-      </c>
-      <c r="O11" t="n">
-        <v>165</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>23</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.625</v>
+        <v>36.75</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>17|19|24|27|38|40|33</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M12" t="n">
         <v>40</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="O12" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.35227272727273</v>
+        <v>36.47727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>17|20|24|29|39|40|7</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.75</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|34</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
         <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.75</v>
+        <v>48.8667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
         <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
+        <v>41</v>
+      </c>
+      <c r="M4" t="n">
         <v>44</v>
-      </c>
-      <c r="M4" t="n">
-        <v>49</v>
       </c>
       <c r="N4" t="n">
         <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.75</v>
+        <v>43.8667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|26</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" t="n">
         <v>19</v>
       </c>
-      <c r="J5" t="n">
-        <v>20</v>
-      </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L5" t="n">
         <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.25</v>
+        <v>41.3667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>7|19|20|30|44|45|15</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
+        <v>6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>143</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
         <v>32</v>
-      </c>
-      <c r="O6" t="n">
-        <v>157</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>40</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.75</v>
+        <v>39.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|32</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.75</v>
+        <v>38.8667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
         <v>19</v>
@@ -1192,13 +1192,13 @@
         <v>31</v>
       </c>
       <c r="M8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.03571428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.5</v>
+        <v>37.6167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.08333333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|33</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1471,25 +1471,25 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>163</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.75</v>
+        <v>36.8667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L12" t="n">
+        <v>41</v>
+      </c>
+      <c r="M12" t="n">
+        <v>44</v>
+      </c>
+      <c r="N12" t="n">
         <v>30</v>
       </c>
-      <c r="L12" t="n">
-        <v>31</v>
-      </c>
-      <c r="M12" t="n">
-        <v>40</v>
-      </c>
-      <c r="N12" t="n">
-        <v>41</v>
-      </c>
       <c r="O12" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.47727272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.9333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
         <v>17</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.8667</v>
+        <v>48.9333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>17|19|24|26|38|45|39</t>
+          <t>1|17|24|28|41|44|47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
         <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
         <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.8667</v>
+        <v>43.9333</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>14|17|19|30|41|44|26</t>
+          <t>2|16|19|37|44|49|26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
         <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.3667</v>
+        <v>41.4333</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|24</t>
+          <t>7|19|20|30|44|45|15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -984,25 +984,25 @@
         <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.8667</v>
+        <v>39.9333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.8667</v>
+        <v>38.9333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.15241428571429</v>
+        <v>38.21901428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|7</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.6167</v>
+        <v>37.6833</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
+        <v>40</v>
+      </c>
+      <c r="L10" t="n">
+        <v>43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" t="n">
         <v>33</v>
       </c>
-      <c r="L10" t="n">
-        <v>38</v>
-      </c>
-      <c r="M10" t="n">
-        <v>41</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
       <c r="O10" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.20003333333333</v>
+        <v>37.26663333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>2|9|24|40|43|45|33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.8667</v>
+        <v>36.9333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L12" t="n">
         <v>31</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
+        <v>40</v>
+      </c>
+      <c r="N12" t="n">
         <v>41</v>
       </c>
-      <c r="M12" t="n">
-        <v>44</v>
-      </c>
-      <c r="N12" t="n">
-        <v>30</v>
-      </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.59397272727273</v>
+        <v>36.66057272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-28 22:50:47</t>
+          <t>2026-05-30 03:12:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-30 03:12:42</t>
+          <t>2026-05-30 10:41:38</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.9333</v>
+        <v>74.6875</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|42</t>
+          <t>1|3|5|44|46|49|17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
         <v>41</v>
       </c>
       <c r="M3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="O3" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.9333</v>
+        <v>48.6875</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|17|24|28|41|44|47</t>
+          <t>5|13|24|30|41|48|28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.9333</v>
+        <v>43.6875</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|26</t>
+          <t>17|19|24|30|39|40|45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.4333</v>
+        <v>41.1875</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>7|19|20|30|44|45|15</t>
+          <t>3|9|14|26|40|41|11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
+        <v>17</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27</v>
+      </c>
+      <c r="L6" t="n">
+        <v>38</v>
+      </c>
+      <c r="M6" t="n">
+        <v>41</v>
+      </c>
+      <c r="N6" t="n">
         <v>18</v>
       </c>
-      <c r="J6" t="n">
-        <v>19</v>
-      </c>
-      <c r="K6" t="n">
-        <v>30</v>
-      </c>
-      <c r="L6" t="n">
-        <v>44</v>
-      </c>
-      <c r="M6" t="n">
-        <v>45</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
       <c r="O6" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.9333</v>
+        <v>39.6875</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>14|17|24|27|38|41|18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O7" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.9333</v>
+        <v>38.6875</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>5|16|24|34|39|45|17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M8" t="n">
+        <v>40</v>
+      </c>
+      <c r="N8" t="n">
         <v>41</v>
       </c>
-      <c r="N8" t="n">
-        <v>4</v>
-      </c>
       <c r="O8" t="n">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.21901428571429</v>
+        <v>37.97321428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>3|9|13|26|30|40|41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" t="n">
         <v>17</v>
       </c>
-      <c r="I9" t="n">
-        <v>19</v>
-      </c>
-      <c r="J9" t="n">
-        <v>24</v>
-      </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.6833</v>
+        <v>37.4375</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>10|13|17|40|41|44|30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N10" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.26663333333333</v>
+        <v>37.02083333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|33</t>
+          <t>17|19|24|26|34|39|3</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1471,25 +1471,25 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
         <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
         <v>151</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.9333</v>
+        <v>36.6875</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>1|14|24|26|41|45|9</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>
@@ -1569,37 +1569,37 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="M12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>169</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
         <v>40</v>
-      </c>
-      <c r="N12" t="n">
-        <v>41</v>
-      </c>
-      <c r="O12" t="n">
-        <v>147</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>37</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.66057272727272</v>
+        <v>36.41477272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>5|14|24|38|43|45|9</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-30 10:41:38</t>
+          <t>2026-05-30 14:19:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.6875</v>
+        <v>74.7333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|17</t>
+          <t>1|3|5|44|46|49|30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6875</v>
+        <v>48.7333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6875</v>
+        <v>43.7333</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1875</v>
+        <v>41.2333</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6875</v>
+        <v>39.7333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6875</v>
+        <v>38.7333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.97321428571428</v>
+        <v>38.01901428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4375</v>
+        <v>37.4833</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.02083333333333</v>
+        <v>37.06663333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6875</v>
+        <v>36.7333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.41477272727273</v>
+        <v>36.46057272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-30 14:19:48</t>
+          <t>2026-05-31 11:23:02</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.7333</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|30</t>
+          <t>1|3|5|44|46|49|46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,16 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L3" t="n">
         <v>41</v>
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.7333</v>
+        <v>48.6</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|28</t>
+          <t>9|14|17|40|41|48|29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -785,10 +785,10 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
@@ -797,16 +797,16 @@
         <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="O4" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.7333</v>
+        <v>43.6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>17|19|24|30|39|40|45</t>
+          <t>5|13|24|30|41|48|28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="O5" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.2333</v>
+        <v>41.1</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|9|14|26|40|41|11</t>
+          <t>9|16|19|31|40|44|42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="O6" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.7333</v>
+        <v>39.6</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>14|17|24|27|38|41|18</t>
+          <t>17|19|24|30|39|40|45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N7" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.7333</v>
+        <v>38.6</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|16|24|34|39|45|17</t>
+          <t>13|17|20|30|40|41|6</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O8" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.01901428571428</v>
+        <v>37.88571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|9|13|26|30|40|41</t>
+          <t>9|16|22|31|44|45|37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
+        <v>19</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26</v>
+      </c>
+      <c r="L9" t="n">
+        <v>31</v>
+      </c>
+      <c r="M9" t="n">
+        <v>45</v>
+      </c>
+      <c r="N9" t="n">
         <v>13</v>
       </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>40</v>
-      </c>
-      <c r="L9" t="n">
-        <v>41</v>
-      </c>
-      <c r="M9" t="n">
-        <v>44</v>
-      </c>
-      <c r="N9" t="n">
-        <v>30</v>
-      </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4833</v>
+        <v>37.35</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>10|13|17|40|41|44|30</t>
+          <t>14|19|24|26|31|45|13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1385,16 +1385,16 @@
         <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M10" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.06663333333333</v>
+        <v>36.93333333333334</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>17|19|24|26|34|39|3</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1471,37 +1471,37 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
+        <v>40</v>
+      </c>
+      <c r="M11" t="n">
+        <v>47</v>
+      </c>
+      <c r="N11" t="n">
+        <v>48</v>
+      </c>
+      <c r="O11" t="n">
+        <v>167</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>41</v>
-      </c>
-      <c r="M11" t="n">
-        <v>45</v>
-      </c>
-      <c r="N11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>151</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>44</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.7333</v>
+        <v>36.6</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1|14|24|26|41|45|9</t>
+          <t>6|19|24|31|40|47|48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>
@@ -1569,25 +1569,25 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L12" t="n">
         <v>38</v>
       </c>
-      <c r="L12" t="n">
-        <v>43</v>
-      </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>169</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.46057272727273</v>
+        <v>36.32727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5|14|24|38|43|45|9</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-05-31 11:23:02</t>
+          <t>2026-06-01 09:02:21</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.59999999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|46</t>
+          <t>1|3|5|44|46|49|37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,16 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
         <v>41</v>
@@ -705,10 +705,10 @@
         <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6</v>
+        <v>48.6667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9|14|17|40|41|48|29</t>
+          <t>5|13|24|30|41|48|28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -788,25 +788,25 @@
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>41</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>48</v>
       </c>
-      <c r="N4" t="n">
-        <v>28</v>
-      </c>
       <c r="O4" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6</v>
+        <v>43.6667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|28</t>
+          <t>5|16|17|26|38|41|48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
+        <v>26</v>
+      </c>
+      <c r="L5" t="n">
         <v>31</v>
       </c>
-      <c r="L5" t="n">
-        <v>40</v>
-      </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1</v>
+        <v>41.1667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|16|19|31|40|44|42</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -981,25 +981,25 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" t="n">
         <v>17</v>
-      </c>
-      <c r="I6" t="n">
-        <v>19</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="O6" t="n">
         <v>169</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6</v>
+        <v>39.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>17|19|24|30|39|40|45</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>17</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N7" t="n">
         <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6</v>
+        <v>38.6667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>13|17|20|30|40|41|6</t>
+          <t>1|17|24|26|38|39|6</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
         <v>9</v>
       </c>
-      <c r="I8" t="n">
-        <v>16</v>
-      </c>
       <c r="J8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N8" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O8" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.88571428571429</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>9|16|22|31|44|45|37</t>
+          <t>3|9|24|32|40|43|41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1275,25 +1275,25 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
         <v>159</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.35</v>
+        <v>37.4167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>14|19|24|26|31|45|13</t>
+          <t>2|16|24|31|39|47|14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="n">
         <v>17</v>
       </c>
-      <c r="I10" t="n">
-        <v>19</v>
-      </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
+        <v>31</v>
+      </c>
+      <c r="L10" t="n">
+        <v>40</v>
+      </c>
+      <c r="M10" t="n">
+        <v>44</v>
+      </c>
+      <c r="N10" t="n">
         <v>26</v>
       </c>
-      <c r="L10" t="n">
-        <v>31</v>
-      </c>
-      <c r="M10" t="n">
-        <v>46</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
       <c r="O10" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.93333333333334</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>9|17|20|31|40|44|26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
+        <v>13</v>
+      </c>
+      <c r="J11" t="n">
         <v>19</v>
       </c>
-      <c r="J11" t="n">
-        <v>24</v>
-      </c>
       <c r="K11" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L11" t="n">
         <v>40</v>
       </c>
       <c r="M11" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6</v>
+        <v>36.6667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|19|24|31|40|47|48</t>
+          <t>9|13|19|34|40|44|6</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>
@@ -1569,25 +1569,25 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O12" t="n">
         <v>169</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.32727272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>5|14|24|38|43|45|9</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-01 09:02:21</t>
+          <t>2026-06-01 20:59:44</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|37</t>
+          <t>1|3|5|44|46|49|47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
+        <v>40</v>
+      </c>
+      <c r="M3" t="n">
         <v>41</v>
       </c>
-      <c r="M3" t="n">
-        <v>48</v>
-      </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6667</v>
+        <v>48.8</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|28</t>
+          <t>14|19|24|31|40|41|45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6667</v>
+        <v>43.8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5|16|17|26|38|41|48</t>
+          <t>16|17|19|31|36|44|1</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1667</v>
+        <v>41.3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6667</v>
+        <v>39.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6667</v>
+        <v>38.8</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1|17|24|26|38|39|6</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L8" t="n">
         <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N8" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.95241428571428</v>
+        <v>38.08571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|9|24|32|40|43|41</t>
+          <t>5|6|13|30|40|41|17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4167</v>
+        <v>37.55</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2|16|24|31|39|47|14</t>
+          <t>5|16|17|34|36|49|8</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
         <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.00003333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9|17|20|31|40|44|26</t>
+          <t>9|17|24|26|34|41|12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="O11" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6667</v>
+        <v>36.8</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9|13|19|34|40|44|6</t>
+          <t>6|19|24|26|33|41|47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.39397272727273</v>
+        <v>36.52727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5|14|24|38|43|45|9</t>
+          <t>9|13|19|34|40|44|6</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-01 20:59:44</t>
+          <t>2026-06-02 18:38:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.8</v>
+        <v>74.5333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|47</t>
+          <t>1|3|5|44|46|49|45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.8</v>
+        <v>48.5333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -785,10 +785,10 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
         <v>19</v>
@@ -797,16 +797,16 @@
         <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
         <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.8</v>
+        <v>43.5333</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>16|17|19|31|36|44|1</t>
+          <t>9|18|19|31|40|44|24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -883,10 +883,10 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
@@ -895,16 +895,16 @@
         <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
         <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="O5" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.3</v>
+        <v>41.0333</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>5|9|24|26|44|45|42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
         <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O6" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.8</v>
+        <v>39.5333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>7|19|24|31|38|40|15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
         <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="O7" t="n">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.8</v>
+        <v>38.5333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>5|6|13|30|40|41|16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
         <v>17</v>
       </c>
       <c r="O8" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.08571428571428</v>
+        <v>37.81901428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5|6|13|30|40|41|17</t>
+          <t>6|9|19|42|44|45|17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="O9" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.55</v>
+        <v>37.2833</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|16|17|34|36|49|8</t>
+          <t>2|9|24|40|43|45|33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
         <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="O10" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.13333333333333</v>
+        <v>36.86663333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9|17|24|26|34|41|12</t>
+          <t>9|13|16|38|40|41|35</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L11" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="N11" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.8</v>
+        <v>36.5333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|19|24|26|33|41|47</t>
+          <t>3|17|20|40|41|48|10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M12" t="n">
         <v>34</v>
       </c>
-      <c r="L12" t="n">
-        <v>40</v>
-      </c>
-      <c r="M12" t="n">
-        <v>44</v>
-      </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.52727272727273</v>
+        <v>36.26057272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9|13|19|34|40|44|6</t>
+          <t>16|17|24|29|31|34|10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-02 18:38:28</t>
+          <t>2026-06-03 19:09:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5333</v>
+        <v>74.6875</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|45</t>
+          <t>1|3|5|44|46|49|39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
         <v>19</v>
@@ -696,16 +696,16 @@
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O3" t="n">
         <v>169</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.5333</v>
+        <v>48.6875</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>14|19|24|31|40|41|45</t>
+          <t>9|19|24|28|44|45|49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -785,19 +785,19 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
         <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
         <v>44</v>
@@ -806,7 +806,7 @@
         <v>24</v>
       </c>
       <c r="O4" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.5333</v>
+        <v>43.6875</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9|18|19|31|40|44|24</t>
+          <t>17|19|20|31|38|44|24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="O5" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.0333</v>
+        <v>41.1875</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5|9|24|26|44|45|42</t>
+          <t>9|14|19|38|40|41|12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
         <v>19</v>
@@ -990,19 +990,19 @@
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
         <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
         <v>15</v>
       </c>
       <c r="O6" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.5333</v>
+        <v>39.6875</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>7|19|24|31|38|40|15</t>
+          <t>14|19|24|27|38|41|15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1079,16 +1079,16 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
         <v>40</v>
@@ -1097,10 +1097,10 @@
         <v>41</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.5333</v>
+        <v>38.6875</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|6|13|30|40|41|16</t>
+          <t>11|19|24|26|40|41|5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
         <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N8" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O8" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.81901428571428</v>
+        <v>37.97321428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|9|19|42|44|45|17</t>
+          <t>9|13|19|32|38|40|29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
+        <v>31</v>
+      </c>
+      <c r="L9" t="n">
+        <v>32</v>
+      </c>
+      <c r="M9" t="n">
         <v>40</v>
       </c>
-      <c r="L9" t="n">
-        <v>43</v>
-      </c>
-      <c r="M9" t="n">
-        <v>45</v>
-      </c>
       <c r="N9" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="O9" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.2833</v>
+        <v>37.4375</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|33</t>
+          <t>11|19|24|31|32|40|42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1373,37 +1373,37 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
         <v>9</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
+        <v>24</v>
+      </c>
+      <c r="K10" t="n">
+        <v>26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>38</v>
+      </c>
+      <c r="M10" t="n">
+        <v>43</v>
+      </c>
+      <c r="N10" t="n">
         <v>13</v>
       </c>
-      <c r="J10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="O10" t="n">
+        <v>145</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>38</v>
-      </c>
-      <c r="L10" t="n">
-        <v>40</v>
-      </c>
-      <c r="M10" t="n">
-        <v>41</v>
-      </c>
-      <c r="N10" t="n">
-        <v>35</v>
-      </c>
-      <c r="O10" t="n">
-        <v>157</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>32</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.86663333333333</v>
+        <v>37.02083333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9|13|16|38|40|41|35</t>
+          <t>5|9|24|26|38|43|13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.5333</v>
+        <v>36.6875</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|17|20|40|41|48|10</t>
+          <t>1|7|24|26|38|45|6</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.26057272727273</v>
+        <v>36.41477272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>16|17|24|29|31|34|10</t>
+          <t>9|11|14|40|44|45|39</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-03 19:09:42</t>
+          <t>2026-06-04 14:28:51</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.6875</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|39</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
         <v>19</v>
@@ -696,16 +696,16 @@
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
         <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
         <v>169</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6875</v>
+        <v>48.8667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9|19|24|28|44|45|49</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" t="n">
         <v>17</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>19</v>
       </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
         <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6875</v>
+        <v>43.8667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>17|19|20|31|38|44|24</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1875</v>
+        <v>41.3667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|14|19|38|40|41|12</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
         <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6875</v>
+        <v>39.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>14|19|24|27|38|41|15</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1079,37 +1079,37 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>31</v>
+      </c>
+      <c r="O7" t="n">
+        <v>157</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>40</v>
-      </c>
-      <c r="M7" t="n">
-        <v>41</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>161</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>30</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6875</v>
+        <v>38.8667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>11|19|24|26|40|41|5</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1177,25 +1177,25 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
         <v>151</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.97321428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>9|13|19|32|38|40|29</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" t="n">
         <v>19</v>
       </c>
-      <c r="J9" t="n">
-        <v>24</v>
-      </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4375</v>
+        <v>37.6167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>11|19|24|31|32|40|42</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.02083333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>5|9|24|26|38|43|13</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1471,10 +1471,10 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
@@ -1483,16 +1483,16 @@
         <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6875</v>
+        <v>36.8667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1|7|24|26|38|45|6</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
         <v>9</v>
       </c>
-      <c r="I12" t="n">
-        <v>11</v>
-      </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
+        <v>41</v>
+      </c>
+      <c r="M12" t="n">
         <v>44</v>
       </c>
-      <c r="M12" t="n">
-        <v>45</v>
-      </c>
       <c r="N12" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.41477272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9|11|14|40|44|45|39</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-04 14:28:51</t>
+          <t>2026-06-05 14:20:01</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -693,19 +693,19 @@
         <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
         <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="O3" t="n">
         <v>169</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.8667</v>
+        <v>48.6667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>17|19|24|26|38|45|39</t>
+          <t>17|19|20|31|38|44|24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M4" t="n">
         <v>41</v>
       </c>
-      <c r="M4" t="n">
-        <v>44</v>
-      </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.8667</v>
+        <v>43.6667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>14|17|19|30|41|44|26</t>
+          <t>11|19|24|26|40|41|6</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
+        <v>35</v>
+      </c>
+      <c r="M5" t="n">
         <v>44</v>
       </c>
-      <c r="M5" t="n">
-        <v>49</v>
-      </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.3667</v>
+        <v>41.1667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|24</t>
+          <t>17|20|24|29|35|44|14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n">
         <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.8667</v>
+        <v>39.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>14|16|17|34|39|49|7</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
@@ -1091,16 +1091,16 @@
         <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.8667</v>
+        <v>38.6667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>5|21|24|30|38|45|6</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1177,10 +1177,10 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
@@ -1189,16 +1189,16 @@
         <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.15241428571429</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|7</t>
+          <t>5|9|24|26|38|43|13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1275,37 +1275,37 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
+        <v>26</v>
+      </c>
+      <c r="L9" t="n">
+        <v>38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N9" t="n">
+        <v>35</v>
+      </c>
+      <c r="O9" t="n">
+        <v>161</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
         <v>30</v>
-      </c>
-      <c r="L9" t="n">
-        <v>44</v>
-      </c>
-      <c r="M9" t="n">
-        <v>45</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>165</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>36</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.6167</v>
+        <v>37.4167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>11|21|24|26|38|41|35</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
         <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.20003333333333</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>8|19|24|31|40|41|5</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.8667</v>
+        <v>36.6667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>1|23|24|32|38|41|5</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
         <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
         <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.59397272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>9|17|20|31|40|44|23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-05 14:20:01</t>
+          <t>2026-06-06 11:13:24</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|47</t>
+          <t>1|3|5|44|46|49|15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J3" t="n">
         <v>19</v>
       </c>
-      <c r="J3" t="n">
-        <v>20</v>
-      </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6667</v>
+        <v>48.8</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>17|19|20|31|38|44|24</t>
+          <t>9|14|19|38|40|41|12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6667</v>
+        <v>43.8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>11|19|24|26|40|41|6</t>
+          <t>1|16|24|29|38|45|8</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
         <v>44</v>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1667</v>
+        <v>41.3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>17|20|24|29|35|44|14</t>
+          <t>3|9|19|30|40|44|11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
         <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O6" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6667</v>
+        <v>39.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>14|16|17|34|39|49|7</t>
+          <t>1|10|17|38|41|44|15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
         <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6667</v>
+        <v>38.8</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|21|24|30|38|45|6</t>
+          <t>13|17|24|26|38|39|31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.95241428571428</v>
+        <v>38.08571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5|9|24|26|38|43|13</t>
+          <t>3|17|22|38|40|41|32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
         <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4167</v>
+        <v>37.55</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>11|21|24|26|38|41|35</t>
+          <t>8|19|24|31|40|41|5</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>8</v>
       </c>
-      <c r="I10" t="n">
-        <v>19</v>
-      </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.00003333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|19|24|31|40|41|5</t>
+          <t>3|8|9|40|44|45|1</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6667</v>
+        <v>36.8</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1|23|24|32|38|41|5</t>
+          <t>5|17|24|26|44|49|8</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L12" t="n">
         <v>31</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>40</v>
       </c>
-      <c r="M12" t="n">
-        <v>44</v>
-      </c>
       <c r="N12" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="O12" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.39397272727273</v>
+        <v>36.52727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9|17|20|31|40|44|23</t>
+          <t>11|19|24|30|31|40|32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-06 11:13:24</t>
+          <t>2026-06-07 11:31:48</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.8</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|15</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
-        <v>14</v>
-      </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.8</v>
+        <v>48.6667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9|14|19|38|40|41|12</t>
+          <t>3|9|22|38|44|49|43</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="O4" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.8</v>
+        <v>43.6667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1|16|24|29|38|45|8</t>
+          <t>17|19|22|26|31|44|33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.3</v>
+        <v>41.1667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|9|19|30|40|44|11</t>
+          <t>10|19|24|31|40|41|15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L6" t="n">
+        <v>39</v>
+      </c>
+      <c r="M6" t="n">
+        <v>41</v>
+      </c>
+      <c r="N6" t="n">
         <v>17</v>
       </c>
-      <c r="K6" t="n">
-        <v>38</v>
-      </c>
-      <c r="L6" t="n">
-        <v>41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>44</v>
-      </c>
-      <c r="N6" t="n">
-        <v>15</v>
-      </c>
       <c r="O6" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.8</v>
+        <v>39.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1|10|17|38|41|44|15</t>
+          <t>16|20|24|29|39|41|17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
         <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.8</v>
+        <v>38.6667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>13|17|24|26|38|39|31</t>
+          <t>5|22|24|31|38|45|6</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" t="n">
+        <v>27</v>
+      </c>
+      <c r="L8" t="n">
+        <v>31</v>
+      </c>
+      <c r="M8" t="n">
+        <v>44</v>
+      </c>
+      <c r="N8" t="n">
         <v>22</v>
       </c>
-      <c r="K8" t="n">
-        <v>38</v>
-      </c>
-      <c r="L8" t="n">
-        <v>40</v>
-      </c>
-      <c r="M8" t="n">
-        <v>41</v>
-      </c>
-      <c r="N8" t="n">
-        <v>32</v>
-      </c>
       <c r="O8" t="n">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.08571428571428</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|17|22|38|40|41|32</t>
+          <t>6|18|19|27|31|44|22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
         <v>19</v>
@@ -1287,16 +1287,16 @@
         <v>31</v>
       </c>
       <c r="L9" t="n">
+        <v>36</v>
+      </c>
+      <c r="M9" t="n">
         <v>40</v>
       </c>
-      <c r="M9" t="n">
-        <v>41</v>
-      </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.55</v>
+        <v>37.4167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>8|19|24|31|40|41|5</t>
+          <t>11|19|24|31|36|40|14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="O10" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.13333333333333</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|8|9|40|44|45|1</t>
+          <t>9|14|19|26|38|41|42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1471,10 +1471,10 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
@@ -1483,16 +1483,16 @@
         <v>26</v>
       </c>
       <c r="L11" t="n">
+        <v>41</v>
+      </c>
+      <c r="M11" t="n">
         <v>44</v>
       </c>
-      <c r="M11" t="n">
-        <v>49</v>
-      </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.8</v>
+        <v>36.6667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5|17|24|26|44|49|8</t>
+          <t>1|3|24|26|41|44|6</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>
@@ -1578,19 +1578,19 @@
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.52727272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>11|19|24|30|31|40|32</t>
+          <t>11|19|24|27|40|44|7</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-07 11:31:48</t>
+          <t>2026-06-08 17:07:05</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
+        <v>41</v>
+      </c>
+      <c r="M3" t="n">
         <v>44</v>
       </c>
-      <c r="M3" t="n">
-        <v>49</v>
-      </c>
       <c r="N3" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="O3" t="n">
         <v>165</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6667</v>
+        <v>48.5</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|43</t>
+          <t>6|19|24|31|41|44|23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N4" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="O4" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6667</v>
+        <v>43.5</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>17|19|22|26|31|44|33</t>
+          <t>3|9|22|38|44|49|43</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
         <v>19</v>
@@ -892,19 +892,19 @@
         <v>24</v>
       </c>
       <c r="K5" t="n">
+        <v>27</v>
+      </c>
+      <c r="L5" t="n">
         <v>31</v>
       </c>
-      <c r="L5" t="n">
-        <v>40</v>
-      </c>
       <c r="M5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="O5" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1667</v>
+        <v>41</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>10|19|24|31|40|41|15</t>
+          <t>14|19|24|27|31|44|35</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
         <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O6" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6667</v>
+        <v>39.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>16|20|24|29|39|41|17</t>
+          <t>10|19|24|31|40|41|15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6667</v>
+        <v>38.5</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|22|24|31|38|45|6</t>
+          <t>11|17|24|26|44|45|12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
         <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.95241428571428</v>
+        <v>37.78571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|18|19|27|31|44|22</t>
+          <t>1|17|20|31|38|44|23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
+        <v>16</v>
+      </c>
+      <c r="K9" t="n">
+        <v>38</v>
+      </c>
+      <c r="L9" t="n">
+        <v>41</v>
+      </c>
+      <c r="M9" t="n">
+        <v>45</v>
+      </c>
+      <c r="N9" t="n">
         <v>24</v>
       </c>
-      <c r="K9" t="n">
-        <v>31</v>
-      </c>
-      <c r="L9" t="n">
-        <v>36</v>
-      </c>
-      <c r="M9" t="n">
-        <v>40</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14</v>
-      </c>
       <c r="O9" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4167</v>
+        <v>37.25</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|14</t>
+          <t>1|2|16|38|41|45|24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.00003333333333</v>
+        <v>36.83333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9|14|19|26|38|41|42</t>
+          <t>9|11|24|31|40|44|30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M11" t="n">
         <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6667</v>
+        <v>36.5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1|3|24|26|41|44|6</t>
+          <t>11|19|24|27|40|44|7</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>
@@ -1569,37 +1569,37 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L12" t="n">
+        <v>38</v>
+      </c>
+      <c r="M12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N12" t="n">
+        <v>21</v>
+      </c>
+      <c r="O12" t="n">
+        <v>159</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
         <v>40</v>
-      </c>
-      <c r="M12" t="n">
-        <v>44</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>165</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>33</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.39397272727273</v>
+        <v>36.22727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>11|19|24|27|40|44|7</t>
+          <t>5|17|20|34|38|45|21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:05</t>
+          <t>2026-06-09 14:12:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5</v>
+        <v>74.4375</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="O3" t="n">
         <v>165</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.5</v>
+        <v>48.4375</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>6|19|24|31|41|44|23</t>
+          <t>3|9|22|38|44|49|43</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
+        <v>36</v>
+      </c>
+      <c r="M4" t="n">
         <v>44</v>
       </c>
-      <c r="M4" t="n">
-        <v>49</v>
-      </c>
       <c r="N4" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.5</v>
+        <v>43.4375</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|43</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41</v>
+        <v>40.9375</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>14|19|24|27|31|44|35</t>
+          <t>2|13|17|30|40|41|9</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
         <v>19</v>
@@ -993,16 +993,16 @@
         <v>31</v>
       </c>
       <c r="L6" t="n">
+        <v>36</v>
+      </c>
+      <c r="M6" t="n">
         <v>40</v>
       </c>
-      <c r="M6" t="n">
-        <v>41</v>
-      </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O6" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.5</v>
+        <v>39.4375</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>10|19|24|31|40|41|15</t>
+          <t>11|19|24|31|36|40|14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
         <v>17</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="O7" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.5</v>
+        <v>38.4375</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>11|17|24|26|44|45|12</t>
+          <t>5|17|20|34|38|45|21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
         <v>23</v>
       </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.78571428571428</v>
+        <v>37.72321428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|17|20|31|38|44|23</t>
+          <t>5|18|19|26|44|45|23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
         <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.25</v>
+        <v>37.1875</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|2|16|38|41|45|24</t>
+          <t>6|16|24|29|43|45|5</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1373,37 +1373,37 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
+        <v>29</v>
+      </c>
+      <c r="L10" t="n">
+        <v>34</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12</v>
+      </c>
+      <c r="O10" t="n">
+        <v>163</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>31</v>
-      </c>
-      <c r="L10" t="n">
-        <v>40</v>
-      </c>
-      <c r="M10" t="n">
-        <v>44</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" t="n">
-        <v>159</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>35</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.83333333333333</v>
+        <v>36.77083333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9|11|24|31|40|44|30</t>
+          <t>14|17|24|29|34|45|12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
         <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="O11" t="n">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.5</v>
+        <v>36.4375</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>11|19|24|27|40|44|7</t>
+          <t>1|13|24|26|41|44|27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
         <v>17</v>
       </c>
-      <c r="J12" t="n">
-        <v>20</v>
-      </c>
       <c r="K12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
         <v>38</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.22727272727273</v>
+        <v>36.16477272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5|17|20|34|38|45|21</t>
+          <t>8|9|17|30|38|41|4</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-09 14:12:28</t>
+          <t>2026-06-10 16:59:53</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4375</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
         <v>38</v>
       </c>
-      <c r="L3" t="n">
-        <v>44</v>
-      </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.4375</v>
+        <v>48.8667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|43</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
         <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
         <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.4375</v>
+        <v>43.8667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.9375</v>
+        <v>41.3667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|13|17|30|40|41|9</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.4375</v>
+        <v>39.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|14</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.4375</v>
+        <v>38.8667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|17|20|34|38|45|21</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
         <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
         <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.72321428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5|18|19|26|44|45|23</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
         <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.1875</v>
+        <v>37.6167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6|16|24|29|43|45|5</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
         <v>17</v>
@@ -1382,19 +1382,19 @@
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.77083333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>14|17|24|29|34|45|12</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1471,10 +1471,10 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
@@ -1483,16 +1483,16 @@
         <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.4375</v>
+        <v>36.8667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1|13|24|26|41|44|27</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L12" t="n">
+        <v>41</v>
+      </c>
+      <c r="M12" t="n">
+        <v>44</v>
+      </c>
+      <c r="N12" t="n">
         <v>30</v>
       </c>
-      <c r="L12" t="n">
-        <v>38</v>
-      </c>
-      <c r="M12" t="n">
-        <v>41</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4</v>
-      </c>
       <c r="O12" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.16477272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>8|9|17|30|38|41|4</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-10 16:59:53</t>
+          <t>2026-06-11 17:59:22</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|42|44|46|49|34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
         <v>17</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
         <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.8667</v>
+        <v>48.5</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>17|19|24|26|38|45|39</t>
+          <t>9|17|24|31|38|44|21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
         <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.8667</v>
+        <v>43.5</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>14|17|19|30|41|44|26</t>
+          <t>9|19|20|31|40|44|5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.3667</v>
+        <v>41</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|24</t>
+          <t>2|13|17|30|40|41|9</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
+        <v>36</v>
+      </c>
+      <c r="M6" t="n">
         <v>40</v>
       </c>
-      <c r="M6" t="n">
-        <v>41</v>
-      </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O6" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.8667</v>
+        <v>39.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>11|19|24|31|36|40|14</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M7" t="n">
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.8667</v>
+        <v>38.5</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>6|16|24|29|43|45|7</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
         <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.15241428571429</v>
+        <v>37.78571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|7</t>
+          <t>5|17|20|34|38|45|22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>18</v>
@@ -1284,7 +1284,7 @@
         <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
         <v>44</v>
@@ -1293,10 +1293,10 @@
         <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.6167</v>
+        <v>37.25</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>5|18|19|26|44|45|23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
         <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.20003333333333</v>
+        <v>36.83333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>14|17|19|34|39|44|12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>13</v>
+      </c>
+      <c r="I11" t="n">
         <v>17</v>
       </c>
-      <c r="I11" t="n">
-        <v>19</v>
-      </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
         <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="O11" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.8667</v>
+        <v>36.5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>13|17|20|30|31|44|23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
         <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.59397272727273</v>
+        <v>36.22727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>6|9|19|31|32|40|10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-11 17:59:22</t>
+          <t>2026-06-12 14:35:03</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5</v>
+        <v>74.4667</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|34</t>
+          <t>1|3|42|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.5</v>
+        <v>48.4667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.5</v>
+        <v>43.4667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41</v>
+        <v>40.9667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.5</v>
+        <v>39.4667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.5</v>
+        <v>38.4667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.78571428571428</v>
+        <v>37.75241428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.25</v>
+        <v>37.2167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.83333333333333</v>
+        <v>36.80003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.5</v>
+        <v>36.4667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.22727272727273</v>
+        <v>36.19397272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-12 14:35:03</t>
+          <t>2026-06-13 11:44:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O2" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4667</v>
+        <v>74.8</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|32</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
-        <v>17</v>
-      </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="O3" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.4667</v>
+        <v>48.8</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9|17|24|31|38|44|21</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
         <v>19</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
+        <v>27</v>
+      </c>
+      <c r="L4" t="n">
         <v>31</v>
-      </c>
-      <c r="L4" t="n">
-        <v>40</v>
       </c>
       <c r="M4" t="n">
         <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.4667</v>
+        <v>43.8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9|19|20|31|40|44|5</t>
+          <t>14|19|24|27|31|44|37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.9667</v>
+        <v>41.3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|13|17|30|40|41|9</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.4667</v>
+        <v>39.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|14</t>
+          <t>2|9|13|38|41|44|5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1079,37 +1079,37 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
+        <v>36</v>
+      </c>
+      <c r="M7" t="n">
+        <v>44</v>
+      </c>
+      <c r="N7" t="n">
+        <v>35</v>
+      </c>
+      <c r="O7" t="n">
+        <v>153</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>43</v>
-      </c>
-      <c r="M7" t="n">
-        <v>45</v>
-      </c>
-      <c r="N7" t="n">
-        <v>7</v>
-      </c>
-      <c r="O7" t="n">
-        <v>163</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.4667</v>
+        <v>38.8</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|16|24|29|43|45|7</t>
+          <t>1|17|24|31|36|44|35</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N8" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.75241428571429</v>
+        <v>38.08571428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>5|17|20|34|38|45|22</t>
+          <t>11|19|24|31|36|40|14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
         <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N9" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="O9" t="n">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.2167</v>
+        <v>37.55</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|18|19|26|44|45|23</t>
+          <t>6|9|19|31|36|40|37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
         <v>34</v>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.80003333333333</v>
+        <v>37.13333333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>14|17|19|34|39|44|12</t>
+          <t>5|9|16|34|44|45|8</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
         <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M11" t="n">
         <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.4667</v>
+        <v>36.8</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>13|17|20|30|31|44|23</t>
+          <t>14|17|19|34|39|44|12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L12" t="n">
         <v>31</v>
       </c>
-      <c r="L12" t="n">
-        <v>32</v>
-      </c>
       <c r="M12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O12" t="n">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.19397272727272</v>
+        <v>36.52727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6|9|19|31|32|40|10</t>
+          <t>13|17|20|30|31|44|23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-13 11:44:13</t>
+          <t>2026-06-14 11:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.8</v>
+        <v>74.7333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|42|44|46|49|17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.8</v>
+        <v>48.7333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M4" t="n">
         <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="O4" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.8</v>
+        <v>43.7333</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>14|19|24|27|31|44|37</t>
+          <t>9|17|24|31|38|44|21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
+        <v>41</v>
+      </c>
+      <c r="L5" t="n">
+        <v>44</v>
+      </c>
+      <c r="M5" t="n">
+        <v>45</v>
+      </c>
+      <c r="N5" t="n">
         <v>31</v>
       </c>
-      <c r="L5" t="n">
-        <v>36</v>
-      </c>
-      <c r="M5" t="n">
-        <v>44</v>
-      </c>
-      <c r="N5" t="n">
-        <v>48</v>
-      </c>
       <c r="O5" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.3</v>
+        <v>41.2333</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>6|7|24|41|44|45|31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -981,16 +981,16 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
         <v>41</v>
@@ -999,10 +999,10 @@
         <v>44</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O6" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.8</v>
+        <v>39.7333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2|9|13|38|41|44|5</t>
+          <t>14|19|20|31|41|44|15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1085,22 +1085,22 @@
         <v>17</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
         <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
         <v>44</v>
       </c>
       <c r="N7" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="O7" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.8</v>
+        <v>38.7333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1|17|24|31|36|44|35</t>
+          <t>1|17|20|31|38|44|23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" t="n">
         <v>19</v>
       </c>
-      <c r="J8" t="n">
-        <v>24</v>
-      </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O8" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.08571428571428</v>
+        <v>38.01901428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|14</t>
+          <t>2|15|19|40|44|45|17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1275,13 +1275,13 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
         <v>31</v>
@@ -1293,10 +1293,10 @@
         <v>40</v>
       </c>
       <c r="N9" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.55</v>
+        <v>37.4833</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6|9|19|31|36|40|37</t>
+          <t>11|19|24|31|36|40|15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="O10" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.13333333333333</v>
+        <v>37.06663333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>5|9|16|34|44|45|8</t>
+          <t>1|15|24|38|40|41|29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
         <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.8</v>
+        <v>36.7333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>14|17|19|34|39|44|12</t>
+          <t>1|9|22|38|42|45|12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N12" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.52727272727273</v>
+        <v>36.46057272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>13|17|20|30|31|44|23</t>
+          <t>6|9|19|31|32|40|11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-14 11:58:04</t>
+          <t>2026-06-15 19:21:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.7333</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|17</t>
+          <t>1|3|5|44|46|49|4</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -687,13 +687,13 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
         <v>38</v>
@@ -702,13 +702,13 @@
         <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.7333</v>
+        <v>48.6</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|45</t>
+          <t>1|9|24|38|44|45|4</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
+        <v>29</v>
+      </c>
+      <c r="L4" t="n">
         <v>31</v>
       </c>
-      <c r="L4" t="n">
-        <v>38</v>
-      </c>
       <c r="M4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.7333</v>
+        <v>43.6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9|17|24|31|38|44|21</t>
+          <t>2|16|24|29|31|41|7</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
         <v>44</v>
       </c>
       <c r="M5" t="n">
+        <v>49</v>
+      </c>
+      <c r="N5" t="n">
         <v>45</v>
       </c>
-      <c r="N5" t="n">
-        <v>31</v>
-      </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.2333</v>
+        <v>41.1</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6|7|24|41|44|45|31</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>27</v>
+      </c>
+      <c r="L6" t="n">
+        <v>31</v>
+      </c>
+      <c r="M6" t="n">
+        <v>38</v>
+      </c>
+      <c r="N6" t="n">
+        <v>33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>161</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
         <v>19</v>
-      </c>
-      <c r="J6" t="n">
-        <v>20</v>
-      </c>
-      <c r="K6" t="n">
-        <v>31</v>
-      </c>
-      <c r="L6" t="n">
-        <v>41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>44</v>
-      </c>
-      <c r="N6" t="n">
-        <v>15</v>
-      </c>
-      <c r="O6" t="n">
-        <v>169</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>30</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.7333</v>
+        <v>39.6</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>14|19|20|31|41|44|15</t>
+          <t>19|22|24|27|31|38|33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.7333</v>
+        <v>38.6</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1|17|20|31|38|44|23</t>
+          <t>9|13|24|26|44|45|30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
+        <v>31</v>
+      </c>
+      <c r="L8" t="n">
+        <v>32</v>
+      </c>
+      <c r="M8" t="n">
         <v>40</v>
       </c>
-      <c r="L8" t="n">
-        <v>44</v>
-      </c>
-      <c r="M8" t="n">
-        <v>45</v>
-      </c>
       <c r="N8" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="O8" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.01901428571428</v>
+        <v>37.88571428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|15|19|40|44|45|17</t>
+          <t>11|19|24|31|32|40|43</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
         <v>19</v>
@@ -1284,19 +1284,19 @@
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O9" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4833</v>
+        <v>37.35</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|15</t>
+          <t>14|19|24|29|38|41|17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1373,37 +1373,37 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
+        <v>37</v>
+      </c>
+      <c r="L10" t="n">
+        <v>41</v>
+      </c>
+      <c r="M10" t="n">
+        <v>44</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>163</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>38</v>
-      </c>
-      <c r="L10" t="n">
-        <v>40</v>
-      </c>
-      <c r="M10" t="n">
-        <v>41</v>
-      </c>
-      <c r="N10" t="n">
-        <v>29</v>
-      </c>
-      <c r="O10" t="n">
-        <v>159</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>40</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.06663333333333</v>
+        <v>36.93333333333334</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1|15|24|38|40|41|29</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O11" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.7333</v>
+        <v>36.6</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1|9|22|38|42|45|12</t>
+          <t>5|14|16|34|45|49|25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
         <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="O12" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.46057272727273</v>
+        <v>36.32727272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6|9|19|31|32|40|11</t>
+          <t>6|19|24|31|40|49|38</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-15 19:21:13</t>
+          <t>2026-06-16 19:09:06</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.59999999999999</v>
+        <v>74.4375</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|4</t>
+          <t>1|3|5|44|46|49|21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="L3" t="n">
+        <v>33</v>
+      </c>
+      <c r="M3" t="n">
         <v>44</v>
       </c>
-      <c r="M3" t="n">
-        <v>45</v>
-      </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6</v>
+        <v>48.4375</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1|9|24|38|44|45|4</t>
+          <t>7|16|24|27|33|44|23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="O4" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6</v>
+        <v>43.4375</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2|16|24|29|31|41|7</t>
+          <t>1|9|24|40|44|45|34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -883,25 +883,25 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="O5" t="n">
         <v>165</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1</v>
+        <v>40.9375</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|45</t>
+          <t>5|20|24|30|41|45|13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17</v>
+      </c>
+      <c r="K6" t="n">
+        <v>26</v>
+      </c>
+      <c r="L6" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" t="n">
+        <v>41</v>
+      </c>
+      <c r="N6" t="n">
         <v>22</v>
       </c>
-      <c r="J6" t="n">
-        <v>24</v>
-      </c>
-      <c r="K6" t="n">
-        <v>27</v>
-      </c>
-      <c r="L6" t="n">
-        <v>31</v>
-      </c>
-      <c r="M6" t="n">
-        <v>38</v>
-      </c>
-      <c r="N6" t="n">
-        <v>33</v>
-      </c>
       <c r="O6" t="n">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6</v>
+        <v>39.4375</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>19|22|24|27|31|38|33</t>
+          <t>1|2|17|26|40|41|22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1079,16 +1079,16 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
         <v>44</v>
@@ -1097,10 +1097,10 @@
         <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6</v>
+        <v>38.4375</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>9|13|24|26|44|45|30</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
+        <v>16</v>
+      </c>
+      <c r="J8" t="n">
         <v>19</v>
-      </c>
-      <c r="J8" t="n">
-        <v>24</v>
       </c>
       <c r="K8" t="n">
         <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="O8" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.88571428571429</v>
+        <v>37.72321428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>11|19|24|31|32|40|43</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
         <v>14</v>
       </c>
-      <c r="I9" t="n">
-        <v>19</v>
-      </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N9" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.35</v>
+        <v>37.1875</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>14|19|24|29|38|41|17</t>
+          <t>5|14|16|34|45|49|25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O10" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.93333333333334</v>
+        <v>36.77083333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>11|19|24|31|36|40|15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
         <v>34</v>
       </c>
       <c r="L11" t="n">
+        <v>44</v>
+      </c>
+      <c r="M11" t="n">
         <v>45</v>
       </c>
-      <c r="M11" t="n">
-        <v>49</v>
-      </c>
       <c r="N11" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6</v>
+        <v>36.4375</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5|14|16|34|45|49|25</t>
+          <t>9|16|21|34|44|45|4</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.32727272727273</v>
+        <v>36.16477272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-16 19:09:06</t>
+          <t>2026-06-17 16:58:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4375</v>
+        <v>74.5625</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|21</t>
+          <t>1|3|5|44|46|49|17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
         <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.4375</v>
+        <v>48.5625</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>7|16|24|27|33|44|23</t>
+          <t>16|17|22|31|38|45|23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="N4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="O4" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.4375</v>
+        <v>43.5625</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1|9|24|40|44|45|34</t>
+          <t>16|17|24|29|31|34|27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
+        <v>19</v>
+      </c>
+      <c r="J5" t="n">
         <v>20</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>31</v>
+      </c>
+      <c r="L5" t="n">
+        <v>37</v>
+      </c>
+      <c r="M5" t="n">
+        <v>44</v>
+      </c>
+      <c r="N5" t="n">
         <v>24</v>
       </c>
-      <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>41</v>
-      </c>
-      <c r="M5" t="n">
-        <v>45</v>
-      </c>
-      <c r="N5" t="n">
-        <v>13</v>
-      </c>
       <c r="O5" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.9375</v>
+        <v>41.0625</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5|20|24|30|41|45|13</t>
+          <t>16|19|20|31|37|44|24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -981,13 +981,13 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
         <v>26</v>
@@ -996,13 +996,13 @@
         <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.4375</v>
+        <v>39.5625</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1|2|17|26|40|41|22</t>
+          <t>3|19|24|26|40|45|9</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.4375</v>
+        <v>38.5625</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>6|19|24|30|41|43|23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1177,37 +1177,37 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
-        <v>19</v>
-      </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
+        <v>45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>147</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>44</v>
-      </c>
-      <c r="N8" t="n">
-        <v>48</v>
-      </c>
-      <c r="O8" t="n">
-        <v>155</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>35</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.72321428571428</v>
+        <v>37.84821428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>1|3|16|38|44|45|11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N9" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.1875</v>
+        <v>37.3125</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|14|16|34|45|49|25</t>
+          <t>5|9|24|26|38|43|13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1373,37 +1373,37 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L10" t="n">
+        <v>44</v>
+      </c>
+      <c r="M10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>169</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>36</v>
-      </c>
-      <c r="M10" t="n">
-        <v>40</v>
-      </c>
-      <c r="N10" t="n">
-        <v>15</v>
-      </c>
-      <c r="O10" t="n">
-        <v>161</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>29</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.77083333333333</v>
+        <v>36.89583333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>11|19|24|31|36|40|15</t>
+          <t>9|16|21|34|44|45|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.4375</v>
+        <v>36.5625</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9|16|21|34|44|45|4</t>
+          <t>3|20|24|31|38|41|30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
         <v>19</v>
@@ -1578,19 +1578,19 @@
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="N12" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.16477272727273</v>
+        <v>36.28977272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6|19|24|31|40|49|38</t>
+          <t>14|19|24|26|41|43|6</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-17 16:58:04</t>
+          <t>2026-06-18 16:59:40</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5625</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|17</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,16 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
         <v>38</v>
@@ -705,7 +705,7 @@
         <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
         <v>169</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.5625</v>
+        <v>48.8667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>16|17|22|31|38|45|23</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
         <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.5625</v>
+        <v>43.8667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>16|17|24|29|31|34|27</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -883,22 +883,22 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>16</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>19</v>
       </c>
-      <c r="J5" t="n">
-        <v>20</v>
-      </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
         <v>24</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.0625</v>
+        <v>41.3667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>16|19|20|31|37|44|24</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -981,13 +981,13 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
         <v>26</v>
@@ -996,13 +996,13 @@
         <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.5625</v>
+        <v>39.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|19|24|26|40|45|9</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1079,10 +1079,10 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
@@ -1091,16 +1091,16 @@
         <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.5625</v>
+        <v>38.8667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|19|24|30|41|43|23</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
         <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.84821428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|3|16|38|44|45|11</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.3125</v>
+        <v>37.6167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|9|24|26|38|43|13</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
         <v>4</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.89583333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9|16|21|34|44|45|4</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
+        <v>26</v>
+      </c>
+      <c r="L11" t="n">
         <v>31</v>
       </c>
-      <c r="L11" t="n">
-        <v>38</v>
-      </c>
       <c r="M11" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.5625</v>
+        <v>36.8667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|20|24|31|38|41|30</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
         <v>41</v>
       </c>
       <c r="M12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.28977272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>14|19|24|26|41|43|6</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-18 16:59:40</t>
+          <t>2026-06-19 14:46:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.7333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|5|44|46|49|25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
         <v>19</v>
@@ -696,19 +696,19 @@
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.8667</v>
+        <v>48.7333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>17|19|24|26|38|45|39</t>
+          <t>14|19|24|27|31|44|37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>41</v>
       </c>
-      <c r="M4" t="n">
-        <v>44</v>
-      </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.8667</v>
+        <v>43.7333</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>14|17|19|30|41|44|26</t>
+          <t>2|17|22|31|38|41|23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" t="n">
         <v>16</v>
       </c>
-      <c r="J5" t="n">
-        <v>19</v>
-      </c>
       <c r="K5" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
         <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.3667</v>
+        <v>41.2333</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|24</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
+        <v>41</v>
+      </c>
+      <c r="M6" t="n">
+        <v>45</v>
+      </c>
+      <c r="N6" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>165</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
         <v>40</v>
-      </c>
-      <c r="M6" t="n">
-        <v>41</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>143</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>32</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.8667</v>
+        <v>39.7333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>5|20|24|30|41|45|48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
+        <v>37</v>
+      </c>
+      <c r="M7" t="n">
         <v>44</v>
       </c>
-      <c r="M7" t="n">
-        <v>45</v>
-      </c>
       <c r="N7" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.8667</v>
+        <v>38.7333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>16|19|20|31|37|44|26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" t="n">
+        <v>38</v>
+      </c>
+      <c r="L8" t="n">
+        <v>41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>44</v>
+      </c>
+      <c r="N8" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="n">
-        <v>19</v>
-      </c>
-      <c r="J8" t="n">
-        <v>24</v>
-      </c>
-      <c r="K8" t="n">
-        <v>26</v>
-      </c>
-      <c r="L8" t="n">
-        <v>31</v>
-      </c>
-      <c r="M8" t="n">
-        <v>45</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7</v>
-      </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.15241428571429</v>
+        <v>38.01901428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|7</t>
+          <t>2|9|13|38|41|44|6</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.6167</v>
+        <v>37.4833</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>8|19|24|31|40|41|6</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
         <v>16</v>
-      </c>
-      <c r="I10" t="n">
-        <v>17</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.20003333333333</v>
+        <v>37.06663333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>3|16|24|31|43|48|5</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.8667</v>
+        <v>36.7333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>5|13|21|30|32|38|7</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
         <v>9</v>
@@ -1578,19 +1578,19 @@
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.59397272727273</v>
+        <v>36.46057272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>7|9|24|34|44|45|16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-19 14:46:37</t>
+          <t>2026-06-20 11:46:11</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
         <v>148</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.7333</v>
+        <v>74.5333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|25</t>
+          <t>1|3|5|44|46|49|29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>16</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17</v>
+      </c>
+      <c r="K3" t="n">
+        <v>34</v>
+      </c>
+      <c r="L3" t="n">
+        <v>44</v>
+      </c>
+      <c r="M3" t="n">
+        <v>45</v>
+      </c>
+      <c r="N3" t="n">
         <v>14</v>
       </c>
-      <c r="I3" t="n">
-        <v>19</v>
-      </c>
-      <c r="J3" t="n">
-        <v>24</v>
-      </c>
-      <c r="K3" t="n">
-        <v>27</v>
-      </c>
-      <c r="L3" t="n">
-        <v>31</v>
-      </c>
-      <c r="M3" t="n">
-        <v>44</v>
-      </c>
-      <c r="N3" t="n">
-        <v>37</v>
-      </c>
       <c r="O3" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.7333</v>
+        <v>48.5333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>14|19|24|27|31|44|37</t>
+          <t>9|16|17|34|44|45|14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
         <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.7333</v>
+        <v>43.5333</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2|17|22|31|38|41|23</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
         <v>31</v>
       </c>
       <c r="L5" t="n">
+        <v>36</v>
+      </c>
+      <c r="M5" t="n">
         <v>44</v>
       </c>
-      <c r="M5" t="n">
-        <v>45</v>
-      </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.2333</v>
+        <v>41.0333</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" t="n">
         <v>41</v>
       </c>
-      <c r="M6" t="n">
-        <v>45</v>
-      </c>
       <c r="N6" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="O6" t="n">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.7333</v>
+        <v>39.5333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5|20|24|30|41|45|48</t>
+          <t>1|2|17|26|40|41|22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
         <v>44</v>
       </c>
       <c r="N7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O7" t="n">
         <v>167</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.7333</v>
+        <v>38.5333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>16|19|20|31|37|44|26</t>
+          <t>16|19|20|31|37|44|25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
         <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.01901428571428</v>
+        <v>37.81901428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|9|13|38|41|44|6</t>
+          <t>9|19|20|31|40|44|5</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
         <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4833</v>
+        <v>37.2833</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>8|19|24|31|40|41|6</t>
+          <t>2|9|13|38|41|44|6</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1373,10 +1373,10 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
@@ -1385,16 +1385,16 @@
         <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M10" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.06663333333333</v>
+        <v>36.86663333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3|16|24|31|43|48|5</t>
+          <t>8|19|24|31|40|41|6</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.7333</v>
+        <v>36.5333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>
@@ -1569,16 +1569,16 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L12" t="n">
         <v>44</v>
@@ -1587,10 +1587,10 @@
         <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.46057272727273</v>
+        <v>36.26057272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>7|9|24|34|44|45|16</t>
+          <t>2|15|19|40|44|45|17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-20 11:46:11</t>
+          <t>2026-06-21 12:32:29</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5333</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|29</t>
+          <t>1|3|42|44|46|49|45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -687,25 +687,25 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
-        <v>16</v>
-      </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
         <v>44</v>
       </c>
       <c r="M3" t="n">
+        <v>49</v>
+      </c>
+      <c r="N3" t="n">
         <v>45</v>
-      </c>
-      <c r="N3" t="n">
-        <v>14</v>
       </c>
       <c r="O3" t="n">
         <v>165</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.5333</v>
+        <v>48.6667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9|16|17|34|44|45|14</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
         <v>31</v>
       </c>
       <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>44</v>
       </c>
-      <c r="M4" t="n">
-        <v>45</v>
-      </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.5333</v>
+        <v>43.6667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>13|17|24|31|38|44|10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" t="n">
         <v>16</v>
-      </c>
-      <c r="J5" t="n">
-        <v>19</v>
       </c>
       <c r="K5" t="n">
         <v>31</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.0333</v>
+        <v>41.1667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n">
         <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.5333</v>
+        <v>39.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1|2|17|26|40|41|22</t>
+          <t>14|16|17|34|39|49|8</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1082,34 +1082,34 @@
         <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
+        <v>29</v>
+      </c>
+      <c r="L7" t="n">
         <v>31</v>
       </c>
-      <c r="L7" t="n">
-        <v>37</v>
-      </c>
       <c r="M7" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N7" t="n">
+        <v>14</v>
+      </c>
+      <c r="O7" t="n">
+        <v>161</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>25</v>
-      </c>
-      <c r="O7" t="n">
-        <v>167</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>28</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.5333</v>
+        <v>38.6667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>16|19|20|31|37|44|25</t>
+          <t>16|20|24|29|31|41|14</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M8" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="O8" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.81901428571428</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>9|19|20|31|40|44|5</t>
+          <t>9|13|24|28|38|41|46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="M9" t="n">
         <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.2833</v>
+        <v>37.4167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2|9|13|38|41|44|6</t>
+          <t>1|16|24|29|35|44|9</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J10" t="n">
         <v>19</v>
-      </c>
-      <c r="J10" t="n">
-        <v>24</v>
       </c>
       <c r="K10" t="n">
         <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="O10" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.86663333333333</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>8|19|24|31|40|41|6</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L11" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.5333</v>
+        <v>36.6667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5|13|21|30|32|38|7</t>
+          <t>9|16|24|35|41|44|4</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O12" t="n">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.26057272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|15|19|40|44|45|17</t>
+          <t>7|16|24|29|30|39|23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-21 12:32:29</t>
+          <t>2026-06-22 19:06:49</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-22 19:06:49</t>
+          <t>2026-06-23 08:10:42</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|45</t>
+          <t>1|3|42|44|46|49|16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N3" t="n">
         <v>45</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6667</v>
+        <v>48.4667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|45</t>
+          <t>16|17|24|29|31|40|45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6667</v>
+        <v>43.4667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1667</v>
+        <v>40.9667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
         <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
+        <v>31</v>
+      </c>
+      <c r="L6" t="n">
+        <v>38</v>
+      </c>
+      <c r="M6" t="n">
+        <v>43</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>161</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
         <v>34</v>
-      </c>
-      <c r="L6" t="n">
-        <v>39</v>
-      </c>
-      <c r="M6" t="n">
-        <v>49</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>169</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>35</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6667</v>
+        <v>39.4667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>14|16|17|34|39|49|8</t>
+          <t>9|16|24|31|38|43|4</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
         <v>16</v>
       </c>
-      <c r="I7" t="n">
-        <v>20</v>
-      </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N7" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6667</v>
+        <v>38.4667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>16|20|24|29|31|41|14</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1180,25 +1180,25 @@
         <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.95241428571428</v>
+        <v>37.75241428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>9|13|24|28|38|41|46</t>
+          <t>9|19|20|31|40|44|6</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
         <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4167</v>
+        <v>37.2167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|16|24|29|35|44|9</t>
+          <t>5|19|24|30|31|44|18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
         <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.00003333333333</v>
+        <v>36.80003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>1|3|24|28|41|44|6</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1471,16 +1471,16 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
         <v>41</v>
@@ -1489,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="O11" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6667</v>
+        <v>36.4667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9|16|24|35|41|44|4</t>
+          <t>3|13|24|26|41|44|23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.39397272727273</v>
+        <v>36.19397272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>7|16|24|29|30|39|23</t>
+          <t>5|17|24|28|44|49|10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-23 08:10:42</t>
+          <t>2026-06-24 08:08:34</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4667</v>
+        <v>74.5333</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|16</t>
+          <t>1|3|42|44|46|49|8</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
         <v>45</v>
       </c>
       <c r="O3" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.4667</v>
+        <v>48.5333</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>16|17|24|29|31|40|45</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.4667</v>
+        <v>43.5333</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>13|17|24|31|38|44|10</t>
+          <t>5|20|24|30|41|45|13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
         <v>31</v>
       </c>
       <c r="L5" t="n">
+        <v>38</v>
+      </c>
+      <c r="M5" t="n">
         <v>44</v>
       </c>
-      <c r="M5" t="n">
-        <v>45</v>
-      </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.9667</v>
+        <v>41.0333</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>13|17|24|31|38|44|10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
         <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.4667</v>
+        <v>39.5333</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|16|24|31|38|43|4</t>
+          <t>14|16|17|34|39|49|7</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="n">
         <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>19</v>
       </c>
       <c r="K7" t="n">
         <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.4667</v>
+        <v>38.5333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1177,10 +1177,10 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="O8" t="n">
         <v>163</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.75241428571429</v>
+        <v>37.81901428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>9|19|20|31|40|44|6</t>
+          <t>7|16|20|31|44|45|43</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
         <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.2167</v>
+        <v>37.2833</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>5|19|24|30|31|44|18</t>
+          <t>1|3|24|28|41|44|6</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1376,34 +1376,34 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>153</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>44</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>141</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.80003333333333</v>
+        <v>36.86663333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1|3|24|28|41|44|6</t>
+          <t>1|9|24|30|44|45|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1471,37 +1471,37 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
+        <v>45</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>143</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
         <v>44</v>
-      </c>
-      <c r="N11" t="n">
-        <v>23</v>
-      </c>
-      <c r="O11" t="n">
-        <v>151</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>41</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.4667</v>
+        <v>36.5333</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|13|24|26|41|44|23</t>
+          <t>1|7|24|28|38|45|6</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="O12" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.19397272727272</v>
+        <v>36.26057272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5|17|24|28|44|49|10</t>
+          <t>5|7|24|38|43|48|33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-24 08:08:34</t>
+          <t>2026-06-25 08:06:43</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -647,12 +647,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|8</t>
+          <t>1|3|42|44|46|49|17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|45</t>
+          <t>5|13|24|38|41|48|9</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
         <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -941,12 +941,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>13|17|24|31|38|44|10</t>
+          <t>1|3|16|38|44|45|10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -981,37 +981,37 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" t="n">
         <v>16</v>
       </c>
-      <c r="J6" t="n">
-        <v>17</v>
-      </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
+        <v>44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>45</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>157</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
         <v>39</v>
-      </c>
-      <c r="M6" t="n">
-        <v>49</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>169</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>35</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>14|16|17|34|39|49|7</t>
+          <t>6|15|16|31|44|45|5</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
+        <v>27</v>
+      </c>
+      <c r="L7" t="n">
         <v>31</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>44</v>
       </c>
-      <c r="M7" t="n">
-        <v>45</v>
-      </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>16|19|22|27|31|44|35</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1177,37 +1177,37 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L8" t="n">
+        <v>41</v>
+      </c>
+      <c r="M8" t="n">
         <v>44</v>
       </c>
-      <c r="M8" t="n">
-        <v>45</v>
-      </c>
       <c r="N8" t="n">
+        <v>6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>141</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>43</v>
-      </c>
-      <c r="O8" t="n">
-        <v>163</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>38</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>7|16|20|31|44|45|43</t>
+          <t>1|3|24|28|41|44|6</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1278,34 +1278,34 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
+        <v>45</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>153</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
         <v>44</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>141</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|3|24|28|41|44|6</t>
+          <t>1|9|24|30|44|45|4</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1376,25 +1376,25 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
         <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1|9|24|30|44|45|4</t>
+          <t>1|7|24|28|38|45|6</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
         <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="O11" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1|7|24|28|38|45|6</t>
+          <t>9|13|24|26|44|45|28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L12" t="n">
         <v>38</v>
       </c>
-      <c r="L12" t="n">
-        <v>43</v>
-      </c>
       <c r="M12" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="O12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5|7|24|38|43|48|33</t>
+          <t>14|19|20|31|38|45|29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-25 08:06:43</t>
+          <t>2026-06-26 08:17:51</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.5333</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|17</t>
+          <t>1|3|42|44|46|49|29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>5</v>
       </c>
-      <c r="I3" t="n">
-        <v>13</v>
-      </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.5333</v>
+        <v>48.6667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>5|13|24|38|41|48|9</t>
+          <t>2|5|9|38|44|45|6</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -785,25 +785,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>41</v>
       </c>
-      <c r="M4" t="n">
-        <v>45</v>
-      </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O4" t="n">
         <v>165</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.5333</v>
+        <v>43.6667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5|20|24|30|41|45|13</t>
+          <t>14|19|24|29|38|41|20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
+        <v>31</v>
+      </c>
+      <c r="L5" t="n">
         <v>38</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>44</v>
       </c>
-      <c r="M5" t="n">
-        <v>45</v>
-      </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="O5" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.0333</v>
+        <v>41.1667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1|3|16|38|44|45|10</t>
+          <t>5|19|22|31|38|44|40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
+        <v>17</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>30</v>
+      </c>
+      <c r="L6" t="n">
+        <v>32</v>
+      </c>
+      <c r="M6" t="n">
+        <v>39</v>
+      </c>
+      <c r="N6" t="n">
         <v>15</v>
       </c>
-      <c r="J6" t="n">
-        <v>16</v>
-      </c>
-      <c r="K6" t="n">
-        <v>31</v>
-      </c>
-      <c r="L6" t="n">
-        <v>44</v>
-      </c>
-      <c r="M6" t="n">
-        <v>45</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
       <c r="O6" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.5333</v>
+        <v>39.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>6|15|16|31|44|45|5</t>
+          <t>13|17|24|30|32|39|15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="n">
         <v>19</v>
       </c>
-      <c r="J7" t="n">
-        <v>22</v>
-      </c>
       <c r="K7" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N7" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="O7" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.5333</v>
+        <v>38.6667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>16|19|22|27|31|44|35</t>
+          <t>2|15|19|40|44|45|17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1177,10 +1177,10 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
@@ -1189,16 +1189,16 @@
         <v>28</v>
       </c>
       <c r="L8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.81901428571428</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1|3|24|28|41|44|6</t>
+          <t>13|15|24|28|44|45|1</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M9" t="n">
         <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.2833</v>
+        <v>37.4167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|9|24|30|44|45|4</t>
+          <t>17|20|24|28|31|45|8</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="O10" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.86663333333333</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1|7|24|28|38|45|6</t>
+          <t>2|17|24|31|33|44|18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
         <v>9</v>
       </c>
-      <c r="I11" t="n">
-        <v>13</v>
-      </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L11" t="n">
+        <v>40</v>
+      </c>
+      <c r="M11" t="n">
         <v>44</v>
       </c>
-      <c r="M11" t="n">
-        <v>45</v>
-      </c>
       <c r="N11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.5333</v>
+        <v>36.6667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9|13|24|26|44|45|28</t>
+          <t>5|9|17|36|40|44|15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L12" t="n">
         <v>38</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="O12" t="n">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.26057272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>14|19|20|31|38|45|29</t>
+          <t>3|5|13|30|38|44|33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-26 08:17:51</t>
+          <t>2026-06-27 07:35:27</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -647,12 +647,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|29</t>
+          <t>1|3|42|44|46|49|8</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L3" t="n">
+        <v>31</v>
+      </c>
+      <c r="M3" t="n">
         <v>44</v>
       </c>
-      <c r="M3" t="n">
-        <v>45</v>
-      </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="O3" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2|5|9|38|44|45|6</t>
+          <t>17|19|22|26|31|44|34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L4" t="n">
         <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -843,12 +843,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>14|19|24|29|38|41|20</t>
+          <t>1|7|24|28|38|45|6</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>5</v>
       </c>
-      <c r="I5" t="n">
-        <v>19</v>
-      </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -941,12 +941,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5|19|22|31|38|44|40</t>
+          <t>2|5|9|38|44|45|6</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O6" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>13|17|24|30|32|39|15</t>
+          <t>14|19|24|29|38|41|17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1079,37 +1079,37 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L7" t="n">
+        <v>45</v>
+      </c>
+      <c r="M7" t="n">
+        <v>49</v>
+      </c>
+      <c r="N7" t="n">
+        <v>24</v>
+      </c>
+      <c r="O7" t="n">
+        <v>163</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>45</v>
-      </c>
-      <c r="N7" t="n">
-        <v>17</v>
-      </c>
-      <c r="O7" t="n">
-        <v>165</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2|15|19|40|44|45|17</t>
+          <t>5|14|16|34|45|49|24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>13|15|24|28|44|45|1</t>
+          <t>17|19|24|26|34|39|8</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
         <v>17</v>
       </c>
-      <c r="I9" t="n">
-        <v>20</v>
-      </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>17|20|24|28|31|45|8</t>
+          <t>2|17|23|26|41|44|7</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1373,37 +1373,37 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="M10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>19</v>
+      </c>
+      <c r="O10" t="n">
+        <v>159</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
         <v>44</v>
-      </c>
-      <c r="N10" t="n">
-        <v>18</v>
-      </c>
-      <c r="O10" t="n">
-        <v>151</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>42</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2|17|24|31|33|44|18</t>
+          <t>1|5|24|40|44|45|19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5|9|17|36|40|44|15</t>
+          <t>3|9|22|42|44|45|7</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>
@@ -1572,25 +1572,25 @@
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M12" t="n">
         <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|5|13|30|38|44|33</t>
+          <t>3|17|24|38|43|44|30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-27 07:35:27</t>
+          <t>2026-06-28 08:11:19</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|8</t>
+          <t>1|3|42|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
         <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O3" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6667</v>
+        <v>48.4667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>17|19|22|26|31|44|34</t>
+          <t>3|9|22|38|44|49|45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6667</v>
+        <v>43.4667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1|7|24|28|38|45|6</t>
+          <t>7|17|24|32|40|41|15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
+        <v>36</v>
+      </c>
+      <c r="M5" t="n">
         <v>44</v>
       </c>
-      <c r="M5" t="n">
-        <v>45</v>
-      </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1667</v>
+        <v>40.9667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|5|9|38|44|45|6</t>
+          <t>9|16|19|31|36|44|48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N6" t="n">
         <v>17</v>
       </c>
       <c r="O6" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6667</v>
+        <v>39.4667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>14|19|24|29|38|41|17</t>
+          <t>3|23|24|28|41|44|17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6667</v>
+        <v>38.4667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|14|16|34|45|49|24</t>
+          <t>16|19|20|31|37|44|27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M8" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.95241428571428</v>
+        <v>37.75241428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>17|19|24|26|34|39|8</t>
+          <t>2|5|9|38|44|45|6</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="O9" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4167</v>
+        <v>37.2167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2|17|23|26|41|44|7</t>
+          <t>14|19|20|31|38|45|32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
         <v>40</v>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M10" t="n">
         <v>45</v>
       </c>
       <c r="N10" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.00003333333333</v>
+        <v>36.80003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1|5|24|40|44|45|19</t>
+          <t>6|14|19|40|41|45|8</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1480,19 +1480,19 @@
         <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="O11" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6667</v>
+        <v>36.4667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|9|22|42|44|45|7</t>
+          <t>3|9|22|30|38|41|49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
         <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.39397272727273</v>
+        <v>36.19397272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|17|24|38|43|44|30</t>
+          <t>7|13|19|32|40|44|6</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-28 08:11:19</t>
+          <t>2026-06-29 09:24:12</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -610,13 +610,13 @@
         <v>32</v>
       </c>
       <c r="O2" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.4667</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|32</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
         <v>38</v>
       </c>
-      <c r="L3" t="n">
-        <v>44</v>
-      </c>
       <c r="M3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O3" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.4667</v>
+        <v>48.8667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3|9|22|38|44|49|45</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
         <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="O4" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.4667</v>
+        <v>43.8667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>7|17|24|32|40|41|15</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>16</v>
@@ -892,19 +892,19 @@
         <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N5" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>40.9667</v>
+        <v>41.3667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9|16|19|31|36|44|48</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" t="n">
         <v>41</v>
       </c>
-      <c r="M6" t="n">
-        <v>44</v>
-      </c>
       <c r="N6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.4667</v>
+        <v>39.8667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3|23|24|28|41|44|17</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L7" t="n">
+        <v>44</v>
+      </c>
+      <c r="M7" t="n">
+        <v>45</v>
+      </c>
+      <c r="N7" t="n">
         <v>31</v>
       </c>
-      <c r="L7" t="n">
-        <v>37</v>
-      </c>
-      <c r="M7" t="n">
-        <v>44</v>
-      </c>
-      <c r="N7" t="n">
-        <v>27</v>
-      </c>
       <c r="O7" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.4667</v>
+        <v>38.8667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>16|19|20|31|37|44|27</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L8" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="M8" t="n">
         <v>45</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.75241428571429</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2|5|9|38|44|45|6</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" t="n">
         <v>19</v>
       </c>
-      <c r="J9" t="n">
-        <v>20</v>
-      </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M9" t="n">
         <v>45</v>
       </c>
       <c r="N9" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.2167</v>
+        <v>37.6167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>14|19|20|31|38|45|32</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L10" t="n">
+        <v>38</v>
+      </c>
+      <c r="M10" t="n">
         <v>41</v>
       </c>
-      <c r="M10" t="n">
-        <v>45</v>
-      </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36.80003333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6|14|19|40|41|45|8</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M11" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N11" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.4667</v>
+        <v>36.8667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3|9|22|30|38|41|49</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M12" t="n">
         <v>44</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.19397272727272</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>7|13|19|32|40|44|6</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-29 09:24:12</t>
+          <t>2026-06-30 08:14:15</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
         <v>44</v>
@@ -607,16 +607,16 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>48</v>
@@ -647,12 +647,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|32</t>
+          <t>1|3|42|44|46|49|14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -687,10 +687,10 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" t="n">
         <v>17</v>
-      </c>
-      <c r="I3" t="n">
-        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
@@ -702,13 +702,13 @@
         <v>38</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N3" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>17|19|24|26|38|45|39</t>
+          <t>13|17|24|26|38|39|34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
         <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>41</v>
       </c>
-      <c r="M4" t="n">
-        <v>44</v>
-      </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -843,12 +843,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>14|17|19|30|41|44|26</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -886,25 +886,25 @@
         <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -941,12 +941,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|24</t>
+          <t>2|5|17|26|38|41|47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,28 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>7|20|24|33|38|45|47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1079,37 +1079,37 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L7" t="n">
         <v>44</v>
       </c>
       <c r="M7" t="n">
+        <v>48</v>
+      </c>
+      <c r="N7" t="n">
+        <v>37</v>
+      </c>
+      <c r="O7" t="n">
+        <v>167</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>45</v>
-      </c>
-      <c r="N7" t="n">
-        <v>31</v>
-      </c>
-      <c r="O7" t="n">
-        <v>157</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>40</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>3|7|24|41|44|48|37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M8" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="O8" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|7</t>
+          <t>7|11|24|38|39|40|34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
         <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>9|18|19|30|44|45|3</t>
+          <t>7|20|24|30|35|39|40</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1373,16 +1373,16 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L10" t="n">
         <v>38</v>
@@ -1391,10 +1391,10 @@
         <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O10" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>7|23|24|30|38|41|16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
         <v>17</v>
-      </c>
-      <c r="I11" t="n">
-        <v>19</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="O11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>6|17|24|35|36|41|33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="O12" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|30</t>
+          <t>5|18|24|38|39|45|49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-06-30 08:14:15</t>
+          <t>2026-07-01 08:43:56</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -607,7 +607,7 @@
         <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O2" t="n">
         <v>185</v>
@@ -643,16 +643,16 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.86669999999999</v>
+        <v>74.66670000000001</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1|3|42|44|46|49|14</t>
+          <t>1|3|42|44|46|49|19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="O3" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -717,7 +717,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -741,16 +741,16 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.8667</v>
+        <v>48.6667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>13|17|24|26|38|39|34</t>
+          <t>9|19|24|28|44|45|49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -785,10 +785,10 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
@@ -800,13 +800,13 @@
         <v>38</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.8667</v>
+        <v>43.6667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|4</t>
+          <t>7|20|24|33|38|45|48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -883,28 +883,28 @@
         <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N5" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="O5" t="n">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="P5" t="n">
         <v>3</v>
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.3667</v>
+        <v>41.1667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2|5|17|26|38|41|47</t>
+          <t>7|11|24|38|39|40|34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
@@ -990,16 +990,16 @@
         <v>24</v>
       </c>
       <c r="K6" t="n">
+        <v>29</v>
+      </c>
+      <c r="L6" t="n">
         <v>33</v>
       </c>
-      <c r="L6" t="n">
-        <v>38</v>
-      </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N6" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="O6" t="n">
         <v>167</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.8667</v>
+        <v>39.6667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>7|20|24|33|38|45|47</t>
+          <t>17|20|24|29|33|44|15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1082,25 +1082,25 @@
         <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
+        <v>31</v>
+      </c>
+      <c r="L7" t="n">
+        <v>38</v>
+      </c>
+      <c r="M7" t="n">
         <v>41</v>
       </c>
-      <c r="L7" t="n">
-        <v>44</v>
-      </c>
-      <c r="M7" t="n">
-        <v>48</v>
-      </c>
       <c r="N7" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="O7" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.8667</v>
+        <v>38.6667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|7|24|41|44|48|37</t>
+          <t>3|20|24|31|38|41|33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1177,28 +1177,28 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O8" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.15241428571429</v>
+        <v>37.95241428571428</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>7|11|24|38|39|40|34</t>
+          <t>3|9|24|40|43|44|45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
         <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M9" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="N9" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.6167</v>
+        <v>37.4167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>7|20|24|30|35|39|40</t>
+          <t>1|16|24|31|43|44|13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1373,10 +1373,10 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
@@ -1385,13 +1385,13 @@
         <v>30</v>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M10" t="n">
         <v>41</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
         <v>163</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.20003333333333</v>
+        <v>37.00003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>7|23|24|30|38|41|16</t>
+          <t>18|19|24|30|31|41|10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>17</v>
@@ -1480,19 +1480,19 @@
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L11" t="n">
         <v>36</v>
       </c>
       <c r="M11" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N11" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.8667</v>
+        <v>36.6667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6|17|24|35|36|41|33</t>
+          <t>5|17|24|34|36|39|6</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>
@@ -1569,28 +1569,28 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="N12" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="O12" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.59397272727273</v>
+        <v>36.39397272727273</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>5|18|24|38|39|45|49</t>
+          <t>3|20|24|31|40|49|21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-07-01 08:43:56</t>
+          <t>2026-07-02 07:59:39</t>
         </is>
       </c>
     </row>

--- a/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
+++ b/data/exports/final_predictions/uk49s_lunchtime_ensemble_predictions.xlsx
@@ -643,7 +643,7 @@
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4667</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>48.6667</v>
+        <v>48.4667</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J4" t="n">
         <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
@@ -839,16 +839,16 @@
         <v>5</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.6667</v>
+        <v>43.4667</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>7|20|24|33|38|45|48</t>
+          <t>6|19|24|29|41|44|4</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -886,34 +886,34 @@
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
+        <v>40</v>
+      </c>
+      <c r="M5" t="n">
+        <v>46</v>
+      </c>
+      <c r="N5" t="n">
+        <v>33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>167</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
         <v>39</v>
-      </c>
-      <c r="M5" t="n">
-        <v>40</v>
-      </c>
-      <c r="N5" t="n">
-        <v>34</v>
-      </c>
-      <c r="O5" t="n">
-        <v>159</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>33</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -937,16 +937,16 @@
         <v>5</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.1667</v>
+        <v>40.9667</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>7|11|24|38|39|40|34</t>
+          <t>7|19|24|31|40|46|33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
@@ -990,16 +990,16 @@
         <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
         <v>167</v>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1035,16 +1035,16 @@
         <v>5</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.6667</v>
+        <v>39.4667</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>17|20|24|29|33|44|15</t>
+          <t>7|20|24|33|38|45|48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1079,28 +1079,28 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
         <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M7" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="n">
         <v>33</v>
       </c>
       <c r="O7" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -1133,16 +1133,16 @@
         <v>5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.6667</v>
+        <v>38.4667</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3|20|24|31|38|41|33</t>
+          <t>5|13|24|30|32|43|33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1177,37 +1177,37 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J8" t="n">
         <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>151</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>43</v>
-      </c>
-      <c r="M8" t="n">
-        <v>44</v>
-      </c>
-      <c r="N8" t="n">
-        <v>45</v>
-      </c>
-      <c r="O8" t="n">
-        <v>163</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>41</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1231,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.95241428571428</v>
+        <v>37.75241428571429</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3|9|24|40|43|44|45</t>
+          <t>2|16|24|31|33|45|15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1275,28 +1275,28 @@
         <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L9" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O9" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
@@ -1305,7 +1305,7 @@
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1329,16 +1329,16 @@
         <v>5</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.4167</v>
+        <v>37.2167</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1|16|24|31|43|44|13</t>
+          <t>5|7|20|30|40|41|19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1373,19 +1373,19 @@
         <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L10" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M10" t="n">
         <v>41</v>
@@ -1394,7 +1394,7 @@
         <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="P10" t="n">
         <v>3</v>
@@ -1403,7 +1403,7 @@
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>37.00003333333333</v>
+        <v>36.80003333333333</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>18|19|24|30|31|41|10</t>
+          <t>6|9|16|31|38|41|10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1471,28 +1471,28 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
         <v>24</v>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M11" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O11" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
@@ -1501,7 +1501,7 @@
         <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1525,16 +1525,16 @@
         <v>5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36.6667</v>
+        <v>36.4667</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>5|17|24|34|36|39|6</t>
+          <t>1|16|24|31|43|44|14</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
@@ -1569,10 +1569,10 @@
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
@@ -1584,13 +1584,13 @@
         <v>40</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O12" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="P12" t="n">
         <v>3</v>
@@ -1599,7 +1599,7 @@
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1623,16 +1623,16 @@
         <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>36.39397272727273</v>
+        <v>36.19397272727272</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3|20|24|31|40|49|21</t>
+          <t>2|7|24|31|40|47|17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-07-02 07:59:39</t>
+          <t>2026-07-03 07:55:33</t>
         </is>
       </c>
     </row>
